--- a/HW-Module/Messergebnisse/ACS712-STROM-SPANNUNG.xlsx
+++ b/HW-Module/Messergebnisse/ACS712-STROM-SPANNUNG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FaRiSmarthome\HW-Module\Messergebnisse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69FD6AB7-85B7-4AB8-863A-7072B192525C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{676FF47B-DA4B-480F-AF91-32AFA5460C14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34669" yWindow="-3369" windowWidth="26300" windowHeight="15935" xr2:uid="{E26B9463-BDE3-4E68-BA94-F255C8AB7DFF}"/>
   </bookViews>
@@ -241,12 +241,276 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-F801-486E-837E-45C570F89A69}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-F801-486E-837E-45C570F89A69}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="7"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000008-F801-486E-837E-45C570F89A69}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="8"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-F801-486E-837E-45C570F89A69}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="9"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000006-F801-486E-837E-45C570F89A69}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="10"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-F801-486E-837E-45C570F89A69}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="11"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000004-F801-486E-837E-45C570F89A69}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="12"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-F801-486E-837E-45C570F89A69}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="13"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-F801-486E-837E-45C570F89A69}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="14"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-F801-486E-837E-45C570F89A69}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="15"/>
+            <c:marker>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000000-F801-486E-837E-45C570F89A69}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:xVal>
             <c:numRef>
-              <c:f>Tabelle1!$A$2:$A$22</c:f>
+              <c:f>Tabelle1!$A$2:$A$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>10</c:v>
                 </c:pt>
@@ -315,10 +579,10 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Tabelle1!$B$2:$B$22</c:f>
+              <c:f>Tabelle1!$B$2:$B$25</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="21"/>
+                <c:ptCount val="24"/>
                 <c:pt idx="0">
                   <c:v>2.6866666666666701</c:v>
                 </c:pt>
@@ -393,6 +657,7 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -412,20 +677,6 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
@@ -563,8 +814,8 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>U</a:t>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t>V</a:t>
                 </a:r>
                 <a:r>
                   <a:rPr lang="en-US" baseline="-25000"/>
@@ -1253,16 +1504,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>172640</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>96439</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>164428</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>177891</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>509587</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>142874</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>501375</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>41015</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1607,10 +1858,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58CDC0C3-CC42-435D-94B9-9B790F9A24E3}">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1741,57 +1992,39 @@
         <v>1.613</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>-5</v>
       </c>
       <c r="B17" s="3">
         <v>1.5369999999999999</v>
       </c>
-      <c r="D17" t="s">
-        <v>5</v>
-      </c>
-      <c r="E17" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>-6</v>
       </c>
       <c r="B18" s="5">
         <v>1.4587454545454499</v>
       </c>
-      <c r="D18" t="s">
-        <v>4</v>
-      </c>
-      <c r="E18" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>-7</v>
       </c>
       <c r="B19" s="5">
         <v>1.38080909090909</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>-8</v>
       </c>
       <c r="B20" s="5">
         <v>1.3028727272727201</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>-9</v>
       </c>
@@ -1799,12 +2032,38 @@
         <v>1.2249363636363599</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>-10</v>
       </c>
       <c r="B22" s="5">
         <v>1.147</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="4" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
